--- a/it_forms/007_crowdstrike_outage_report_form--it_forms.xlsx
+++ b/it_forms/007_crowdstrike_outage_report_form--it_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1003,8 +1003,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="35" customWidth="1" min="1" max="1"/>
-    <col width="47" customWidth="1" min="2" max="2"/>
-    <col width="47" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1032,12 +1032,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1066,12 +1066,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'low',_'label':_'low'}</t>
+          <t>low</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'low', 'label': 'Low'}</t>
+          <t>Low</t>
         </is>
       </c>
     </row>
@@ -1083,12 +1083,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'medium',_'label':_'medium'}</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'medium', 'label': 'Medium'}</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1100,12 +1100,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'high',_'label':_'high'}</t>
+          <t>high</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'high', 'label': 'High'}</t>
+          <t>High</t>
         </is>
       </c>
     </row>
@@ -1117,12 +1117,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1134,12 +1134,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1151,12 +1151,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'johndoe',_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'JohnDoe', 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1168,12 +1168,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'janedoe',_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'JaneDoe', 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'jimmydoe',_'label':_'jimmy_doe'}</t>
+          <t>jimmy_doe</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'JimmyDoe', 'label': 'Jimmy Doe'}</t>
+          <t>Jimmy Doe</t>
         </is>
       </c>
     </row>
@@ -1202,12 +1202,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'johndoe',_'label':_'john_doe'}</t>
+          <t>john_doe</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'JohnDoe', 'label': 'John Doe'}</t>
+          <t>John Doe</t>
         </is>
       </c>
     </row>
@@ -1219,12 +1219,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'janedoe',_'label':_'jane_doe'}</t>
+          <t>jane_doe</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'JaneDoe', 'label': 'Jane Doe'}</t>
+          <t>Jane Doe</t>
         </is>
       </c>
     </row>
@@ -1236,12 +1236,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'jimmydoe',_'label':_'jimmy_doe'}</t>
+          <t>jimmy_doe</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'JimmyDoe', 'label': 'Jimmy Doe'}</t>
+          <t>Jimmy Doe</t>
         </is>
       </c>
     </row>
@@ -1253,12 +1253,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'service_a',_'label':_'service_a'}</t>
+          <t>service_a</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Service A', 'label': 'Service A'}</t>
+          <t>Service A</t>
         </is>
       </c>
     </row>
@@ -1270,12 +1270,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'service_b',_'label':_'service_b'}</t>
+          <t>service_b</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Service B', 'label': 'Service B'}</t>
+          <t>Service B</t>
         </is>
       </c>
     </row>
@@ -1287,12 +1287,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'service_c',_'label':_'service_c'}</t>
+          <t>service_c</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Service C', 'label': 'Service C'}</t>
+          <t>Service C</t>
         </is>
       </c>
     </row>
@@ -1304,12 +1304,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_'network',_'label':_'network'}</t>
+          <t>network</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 'network', 'label': 'Network'}</t>
+          <t>Network</t>
         </is>
       </c>
     </row>
@@ -1321,12 +1321,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_'system',_'label':_'system'}</t>
+          <t>system</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 'system', 'label': 'System'}</t>
+          <t>System</t>
         </is>
       </c>
     </row>
@@ -1338,12 +1338,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_'location1',_'label':_'location_1'}</t>
+          <t>location_1</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 'location1', 'label': 'Location 1'}</t>
+          <t>Location 1</t>
         </is>
       </c>
     </row>
@@ -1355,12 +1355,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_'location2',_'label':_'location_2'}</t>
+          <t>location_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 'location2', 'label': 'Location 2'}</t>
+          <t>Location 2</t>
         </is>
       </c>
     </row>
@@ -1372,12 +1372,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_'location3',_'label':_'location_3'}</t>
+          <t>location_3</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 'location3', 'label': 'Location 3'}</t>
+          <t>Location 3</t>
         </is>
       </c>
     </row>
@@ -1389,12 +1389,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_'once',_'label':_'once'}</t>
+          <t>once</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 'once', 'label': 'Once'}</t>
+          <t>Once</t>
         </is>
       </c>
     </row>
@@ -1406,12 +1406,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_'multiple',_'label':_'multiple'}</t>
+          <t>multiple</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 'multiple', 'label': 'Multiple'}</t>
+          <t>Multiple</t>
         </is>
       </c>
     </row>
@@ -1423,12 +1423,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_false,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': False, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1440,12 +1440,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_true,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': True, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1457,12 +1457,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_'scheduled',_'label':_'scheduled'}</t>
+          <t>scheduled</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 'scheduled', 'label': 'Scheduled'}</t>
+          <t>Scheduled</t>
         </is>
       </c>
     </row>
@@ -1474,12 +1474,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_'unplanned',_'label':_'unplanned'}</t>
+          <t>unplanned</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 'unplanned', 'label': 'Unplanned'}</t>
+          <t>Unplanned</t>
         </is>
       </c>
     </row>
